--- a/JsonConverter/ExcelFiles/SkillData.xlsx
+++ b/JsonConverter/ExcelFiles/SkillData.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="47">
   <si>
     <t>스킬 고유id</t>
   </si>
@@ -37,21 +37,21 @@
     <t>string</t>
   </si>
   <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>float</t>
+  </si>
+  <si>
+    <t>Id</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
     <t>SkillType</t>
   </si>
   <si>
-    <t>int</t>
-  </si>
-  <si>
-    <t>float</t>
-  </si>
-  <si>
-    <t>Id</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
     <t>TargetCount</t>
   </si>
   <si>
@@ -92,13 +92,73 @@
   </si>
   <si>
     <t>찌르기</t>
+  </si>
+  <si>
+    <t>Skill_101</t>
+  </si>
+  <si>
+    <t>베개 휘두르기</t>
+  </si>
+  <si>
+    <t>Skill_102</t>
+  </si>
+  <si>
+    <t>소맷자락 일격</t>
+  </si>
+  <si>
+    <t>Skill_103</t>
+  </si>
+  <si>
+    <t>마력 탄</t>
+  </si>
+  <si>
+    <t>Skill_104</t>
+  </si>
+  <si>
+    <t>방어 태세</t>
+  </si>
+  <si>
+    <t>Skill_105</t>
+  </si>
+  <si>
+    <t>조준 사격</t>
+  </si>
+  <si>
+    <t>Skill_106</t>
+  </si>
+  <si>
+    <t>꿈결 치유</t>
+  </si>
+  <si>
+    <t>Skill_107</t>
+  </si>
+  <si>
+    <t>은빛 반격</t>
+  </si>
+  <si>
+    <t>Skill_108</t>
+  </si>
+  <si>
+    <t>수면 낙인</t>
+  </si>
+  <si>
+    <t>Skill_109</t>
+  </si>
+  <si>
+    <t>별빛 세례</t>
+  </si>
+  <si>
+    <t>Skill_110</t>
+  </si>
+  <si>
+    <t>몽환의 일격</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -108,6 +168,11 @@
     <font>
       <color rgb="FF000000"/>
       <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="5">
@@ -142,7 +207,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -157,6 +222,9 @@
     </xf>
     <xf borderId="0" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -409,27 +477,27 @@
         <v>8</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>10</v>
-      </c>
       <c r="F2" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="2" t="s">
         <v>12</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>13</v>
@@ -556,6 +624,236 @@
         <v>6.0</v>
       </c>
       <c r="G8" s="4">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="D9" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="E9" s="5">
+        <v>5.0</v>
+      </c>
+      <c r="F9" s="5">
+        <v>5.0</v>
+      </c>
+      <c r="G9" s="5">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="D10" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="E10" s="5">
+        <v>4.0</v>
+      </c>
+      <c r="F10" s="5">
+        <v>7.0</v>
+      </c>
+      <c r="G10" s="5">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="D11" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="E11" s="5">
+        <v>6.0</v>
+      </c>
+      <c r="F11" s="5">
+        <v>8.0</v>
+      </c>
+      <c r="G11" s="5">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" s="5">
+        <v>2.0</v>
+      </c>
+      <c r="D12" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="E12" s="5">
+        <v>10.0</v>
+      </c>
+      <c r="F12" s="5">
+        <v>3.0</v>
+      </c>
+      <c r="G12" s="5">
+        <v>6.0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C13" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="D13" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="E13" s="5">
+        <v>5.0</v>
+      </c>
+      <c r="F13" s="5">
+        <v>9.0</v>
+      </c>
+      <c r="G13" s="5">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="C14" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="D14" s="5">
+        <v>3.0</v>
+      </c>
+      <c r="E14" s="5">
+        <v>9.0</v>
+      </c>
+      <c r="F14" s="5">
+        <v>6.0</v>
+      </c>
+      <c r="G14" s="5">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C15" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="D15" s="5">
+        <v>2.0</v>
+      </c>
+      <c r="E15" s="5">
+        <v>7.0</v>
+      </c>
+      <c r="F15" s="5">
+        <v>10.0</v>
+      </c>
+      <c r="G15" s="5">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C16" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="D16" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="E16" s="5">
+        <v>4.0</v>
+      </c>
+      <c r="F16" s="5">
+        <v>12.0</v>
+      </c>
+      <c r="G16" s="5">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C17" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="D17" s="5">
+        <v>3.0</v>
+      </c>
+      <c r="E17" s="5">
+        <v>8.0</v>
+      </c>
+      <c r="F17" s="5">
+        <v>11.0</v>
+      </c>
+      <c r="G17" s="5">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C18" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="D18" s="5">
+        <v>3.0</v>
+      </c>
+      <c r="E18" s="5">
+        <v>10.0</v>
+      </c>
+      <c r="F18" s="5">
+        <v>14.0</v>
+      </c>
+      <c r="G18" s="5">
         <v>0.0</v>
       </c>
     </row>

--- a/JsonConverter/ExcelFiles/SkillData.xlsx
+++ b/JsonConverter/ExcelFiles/SkillData.xlsx
@@ -55,7 +55,7 @@
     <t>TargetCount</t>
   </si>
   <si>
-    <t>CoolTime</t>
+    <t>CoolDown</t>
   </si>
   <si>
     <t>BaseEffect</t>
@@ -175,7 +175,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -196,6 +196,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor rgb="FFFF0000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC0CDEF"/>
         <bgColor rgb="FFC0CDEF"/>
       </patternFill>
@@ -207,7 +213,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -220,7 +226,10 @@
     <xf borderId="0" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -502,7 +511,7 @@
       <c r="D3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="3" t="s">
         <v>14</v>
       </c>
       <c r="F3" s="2" t="s">
@@ -513,347 +522,347 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="D4" s="3">
-        <v>1.0</v>
-      </c>
-      <c r="E4" s="4">
+      <c r="C4" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="D4" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="E4" s="5">
         <v>5.0</v>
       </c>
-      <c r="F4" s="4">
+      <c r="F4" s="5">
         <v>5.0</v>
       </c>
-      <c r="G4" s="4">
+      <c r="G4" s="5">
         <v>0.0</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5" s="4">
         <v>2.0</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D5" s="4">
         <v>3.0</v>
       </c>
-      <c r="E5" s="4">
+      <c r="E5" s="5">
         <v>8.0</v>
       </c>
-      <c r="F5" s="4">
+      <c r="F5" s="5">
         <v>3.0</v>
       </c>
-      <c r="G5" s="4">
+      <c r="G5" s="5">
         <v>5.0</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C6" s="3">
-        <v>1.0</v>
-      </c>
-      <c r="D6" s="3">
+      <c r="C6" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="D6" s="4">
         <v>3.0</v>
       </c>
-      <c r="E6" s="4">
+      <c r="E6" s="5">
         <v>9.0</v>
       </c>
-      <c r="F6" s="4">
+      <c r="F6" s="5">
         <v>4.0</v>
       </c>
-      <c r="G6" s="4">
+      <c r="G6" s="5">
         <v>0.0</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C7" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="D7" s="3">
+      <c r="C7" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="D7" s="4">
         <v>3.0</v>
       </c>
-      <c r="E7" s="4">
+      <c r="E7" s="5">
         <v>8.0</v>
       </c>
-      <c r="F7" s="4">
+      <c r="F7" s="5">
         <v>6.0</v>
       </c>
-      <c r="G7" s="4">
+      <c r="G7" s="5">
         <v>0.0</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="C8" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="D8" s="3">
-        <v>1.0</v>
-      </c>
-      <c r="E8" s="4">
+      <c r="C8" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="D8" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="E8" s="5">
         <v>4.0</v>
       </c>
-      <c r="F8" s="4">
+      <c r="F8" s="5">
         <v>6.0</v>
       </c>
-      <c r="G8" s="4">
+      <c r="G8" s="5">
         <v>0.0</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C9" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="D9" s="5">
-        <v>1.0</v>
-      </c>
-      <c r="E9" s="5">
+      <c r="C9" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="D9" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="E9" s="6">
         <v>5.0</v>
       </c>
-      <c r="F9" s="5">
+      <c r="F9" s="6">
         <v>5.0</v>
       </c>
-      <c r="G9" s="5">
+      <c r="G9" s="6">
         <v>0.0</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C10" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="D10" s="5">
-        <v>1.0</v>
-      </c>
-      <c r="E10" s="5">
+      <c r="C10" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="D10" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="E10" s="6">
         <v>4.0</v>
       </c>
-      <c r="F10" s="5">
+      <c r="F10" s="6">
         <v>7.0</v>
       </c>
-      <c r="G10" s="5">
+      <c r="G10" s="6">
         <v>0.0</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="C11" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="D11" s="5">
-        <v>1.0</v>
-      </c>
-      <c r="E11" s="5">
+      <c r="C11" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="D11" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="E11" s="6">
         <v>6.0</v>
       </c>
-      <c r="F11" s="5">
+      <c r="F11" s="6">
         <v>8.0</v>
       </c>
-      <c r="G11" s="5">
+      <c r="G11" s="6">
         <v>0.0</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="C12" s="5">
+      <c r="C12" s="6">
         <v>2.0</v>
       </c>
-      <c r="D12" s="5">
-        <v>1.0</v>
-      </c>
-      <c r="E12" s="5">
+      <c r="D12" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="E12" s="6">
         <v>10.0</v>
       </c>
-      <c r="F12" s="5">
+      <c r="F12" s="6">
         <v>3.0</v>
       </c>
-      <c r="G12" s="5">
+      <c r="G12" s="6">
         <v>6.0</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="C13" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="D13" s="5">
-        <v>1.0</v>
-      </c>
-      <c r="E13" s="5">
+      <c r="C13" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="D13" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="E13" s="6">
         <v>5.0</v>
       </c>
-      <c r="F13" s="5">
+      <c r="F13" s="6">
         <v>9.0</v>
       </c>
-      <c r="G13" s="5">
+      <c r="G13" s="6">
         <v>0.0</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="C14" s="5">
-        <v>1.0</v>
-      </c>
-      <c r="D14" s="5">
+      <c r="C14" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="D14" s="6">
         <v>3.0</v>
       </c>
-      <c r="E14" s="5">
+      <c r="E14" s="6">
         <v>9.0</v>
       </c>
-      <c r="F14" s="5">
+      <c r="F14" s="6">
         <v>6.0</v>
       </c>
-      <c r="G14" s="5">
+      <c r="G14" s="6">
         <v>0.0</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="C15" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="D15" s="5">
+      <c r="C15" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="D15" s="6">
         <v>2.0</v>
       </c>
-      <c r="E15" s="5">
+      <c r="E15" s="6">
         <v>7.0</v>
       </c>
-      <c r="F15" s="5">
+      <c r="F15" s="6">
         <v>10.0</v>
       </c>
-      <c r="G15" s="5">
+      <c r="G15" s="6">
         <v>0.0</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="C16" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="D16" s="5">
-        <v>1.0</v>
-      </c>
-      <c r="E16" s="5">
+      <c r="C16" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="D16" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="E16" s="6">
         <v>4.0</v>
       </c>
-      <c r="F16" s="5">
+      <c r="F16" s="6">
         <v>12.0</v>
       </c>
-      <c r="G16" s="5">
+      <c r="G16" s="6">
         <v>0.0</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="s">
+      <c r="A17" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="C17" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="D17" s="5">
+      <c r="C17" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="D17" s="6">
         <v>3.0</v>
       </c>
-      <c r="E17" s="5">
+      <c r="E17" s="6">
         <v>8.0</v>
       </c>
-      <c r="F17" s="5">
+      <c r="F17" s="6">
         <v>11.0</v>
       </c>
-      <c r="G17" s="5">
+      <c r="G17" s="6">
         <v>0.0</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="s">
+      <c r="A18" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="C18" s="5">
-        <v>0.0</v>
-      </c>
-      <c r="D18" s="5">
+      <c r="C18" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="D18" s="6">
         <v>3.0</v>
       </c>
-      <c r="E18" s="5">
+      <c r="E18" s="6">
         <v>10.0</v>
       </c>
-      <c r="F18" s="5">
+      <c r="F18" s="6">
         <v>14.0</v>
       </c>
-      <c r="G18" s="5">
+      <c r="G18" s="6">
         <v>0.0</v>
       </c>
     </row>
